--- a/plugins/pd-rule-extractor/skills/pd-rule-extractor/examples/sample-output.xlsx
+++ b/plugins/pd-rule-extractor/skills/pd-rule-extractor/examples/sample-output.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>ICF签署日期 &lt;= 首次方案操作日期</t>
+          <t>DATEDIFF(ICF.ICFDAT, SV.SVSTDTC, 'day') &gt; 0</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>ICF签署日期, 首次方案操作日期</t>
+          <t>ICF.ICFDAT, SV.SVSTDTC</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>18 &lt;= 年龄 &lt;= 65</t>
+          <t>DM.AGE NOT BETWEEN 18 AND 65</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>出生日期, 筛选日期, 年龄</t>
+          <t>DM.AGE</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>abs(访视实际日期 - 访视计划日期) &lt;= 3天</t>
+          <t>ABS(DATEDIFF(VISIT.VISDAT, VISIT.PLANNDT, 'day')) &gt; 3</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>访视实际日期, 访视计划日期</t>
+          <t>VISIT.VISDAT, VISIT.PLANNDT</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0.8 &lt;= 实际服药量 / 应服药量 &lt;= 1.2</t>
+          <t>(EX.ACTDOSE / EX.PRESCRIBED_DOSE) NOT BETWEEN 0.8 AND 1.2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>实际服药量, 应服药量</t>
+          <t>EX.ACTDOSE, EX.PRESCRIBED_DOSE</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>合并用药通用名 非空</t>
+          <t>CM.CMTRT IS NULL</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>合并用药通用名</t>
+          <t>CM.CMTRT</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>机器可判定的条件表达式（字段、比较符、阈值、时间窗等）</t>
+          <t>SQL 风格形式化表达式（数据集.变量 全限定、比较符、EXISTS/NOT EXISTS、DATEDIFF 等），可直接作为编写偏离数据拉取代码的依据</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>判定逻辑引用的具体字段或数据点</t>
+          <t>判定逻辑引用的变量（数据集.变量 全限定，逗号分隔，与判定逻辑中出现的变量一致）</t>
         </is>
       </c>
     </row>
